--- a/data/nonACMGPLP_pLoF_allinfo_AA_simplified_with_UniProt_IDs.xlsx
+++ b/data/nonACMGPLP_pLoF_allinfo_AA_simplified_with_UniProt_IDs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yvesgreatti/github/Variant-Effects/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{410C14A2-9496-7146-AC18-5B6CF3FCDAC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A3C2413-B82A-8B49-B434-DBCA9BECE47D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2080" yWindow="6480" windowWidth="35840" windowHeight="20200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -641,12 +641,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -676,11 +682,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1150,7 +1157,7 @@
       <c r="H5" t="s">
         <v>15</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="2" t="s">
         <v>26</v>
       </c>
       <c r="J5" t="s">
@@ -1182,7 +1189,7 @@
       <c r="H6" t="s">
         <v>15</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="2" t="s">
         <v>29</v>
       </c>
       <c r="J6" t="s">
@@ -1502,7 +1509,7 @@
       <c r="H16" t="s">
         <v>15</v>
       </c>
-      <c r="I16" t="s">
+      <c r="I16" s="2" t="s">
         <v>65</v>
       </c>
       <c r="J16" t="s">
@@ -1534,7 +1541,7 @@
       <c r="H17" t="s">
         <v>15</v>
       </c>
-      <c r="I17" t="s">
+      <c r="I17" s="2" t="s">
         <v>68</v>
       </c>
       <c r="J17" t="s">
@@ -1566,7 +1573,7 @@
       <c r="H18" t="s">
         <v>15</v>
       </c>
-      <c r="I18" t="s">
+      <c r="I18" s="2" t="s">
         <v>72</v>
       </c>
       <c r="J18" t="s">
@@ -1630,7 +1637,7 @@
       <c r="H20" t="s">
         <v>15</v>
       </c>
-      <c r="I20" t="s">
+      <c r="I20" s="2" t="s">
         <v>83</v>
       </c>
       <c r="J20" t="s">
@@ -1694,7 +1701,7 @@
       <c r="H22" t="s">
         <v>15</v>
       </c>
-      <c r="I22" t="s">
+      <c r="I22" s="2" t="s">
         <v>90</v>
       </c>
       <c r="J22" t="s">
@@ -1726,7 +1733,7 @@
       <c r="H23" t="s">
         <v>15</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" s="2" t="s">
         <v>93</v>
       </c>
       <c r="J23" t="s">
@@ -1758,7 +1765,7 @@
       <c r="H24" t="s">
         <v>15</v>
       </c>
-      <c r="I24" t="s">
+      <c r="I24" s="2" t="s">
         <v>87</v>
       </c>
       <c r="J24" t="s">
@@ -1822,7 +1829,7 @@
       <c r="H26" t="s">
         <v>15</v>
       </c>
-      <c r="I26" t="s">
+      <c r="I26" s="2" t="s">
         <v>105</v>
       </c>
       <c r="J26" t="s">
@@ -1854,7 +1861,7 @@
       <c r="H27" t="s">
         <v>15</v>
       </c>
-      <c r="I27" t="s">
+      <c r="I27" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J27" t="s">
@@ -1918,7 +1925,7 @@
       <c r="H29" t="s">
         <v>15</v>
       </c>
-      <c r="I29" t="s">
+      <c r="I29" s="2" t="s">
         <v>119</v>
       </c>
       <c r="J29" t="s">
@@ -1982,7 +1989,7 @@
       <c r="H31" t="s">
         <v>15</v>
       </c>
-      <c r="I31" t="s">
+      <c r="I31" s="2" t="s">
         <v>126</v>
       </c>
       <c r="J31" t="s">
@@ -2110,7 +2117,7 @@
       <c r="H35" t="s">
         <v>15</v>
       </c>
-      <c r="I35" t="s">
+      <c r="I35" s="2" t="s">
         <v>144</v>
       </c>
       <c r="J35" t="s">
@@ -2398,7 +2405,7 @@
       <c r="H44" t="s">
         <v>15</v>
       </c>
-      <c r="I44" t="s">
+      <c r="I44" s="2" t="s">
         <v>169</v>
       </c>
       <c r="J44" t="s">
@@ -2590,7 +2597,7 @@
       <c r="H50" t="s">
         <v>15</v>
       </c>
-      <c r="I50" t="s">
+      <c r="I50" s="2" t="s">
         <v>183</v>
       </c>
       <c r="J50" t="s">
@@ -2654,7 +2661,7 @@
       <c r="H52" t="s">
         <v>15</v>
       </c>
-      <c r="I52" t="s">
+      <c r="I52" s="2" t="s">
         <v>191</v>
       </c>
       <c r="J52" t="s">
@@ -2686,7 +2693,7 @@
       <c r="H53" t="s">
         <v>15</v>
       </c>
-      <c r="I53" t="s">
+      <c r="I53" s="2" t="s">
         <v>29</v>
       </c>
       <c r="J53" t="s">
